--- a/workbook/historical_events_analysis.xlsx
+++ b/workbook/historical_events_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4187f59888910b2c/Documents/Historical Events Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{10712462-A393-4074-B003-B18B94321660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15600E8C-E1D0-448D-A9A3-7D34B6E79ED9}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{10712462-A393-4074-B003-B18B94321660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99565AAA-54BF-4221-B71E-08D4CFD7FF22}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6D2E873C-0883-4A45-B1D6-516B2229282E}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12075" uniqueCount="4816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12077" uniqueCount="4818">
   <si>
     <t>Sl. No</t>
   </si>
@@ -14516,6 +14516,12 @@
   </si>
   <si>
     <t>Distinct values</t>
+  </si>
+  <si>
+    <t>Rows in duplicate groups</t>
+  </si>
+  <si>
+    <t>Duplicate events (name + year + country)</t>
   </si>
 </sst>
 </file>
@@ -56669,10 +56675,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2440BBC1-080B-4CA4-9F3C-B69FF75F2A45}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.109375" bestFit="1" customWidth="1"/>
@@ -56942,7 +56948,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <v>Outcome</v>
       </c>
@@ -56961,6 +56967,339 @@
       <c r="E17">
         <f>COUNTA(_xlfn.UNIQUE(INDEX(Raw_Data[],0,MATCH(A17,Raw_Data[#Headers],0))))</f>
         <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>4816</v>
+      </c>
+      <c r="B20" cm="1">
+        <f t="array" ref="B20">SUMPRODUCT(--(COUNTIFS(Raw_Data[Name of Incident],Raw_Data[Name of Incident],Raw_Data[Year],Raw_Data[Year],Raw_Data[Country],Raw_Data[Country])&gt;1))</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>4817</v>
+      </c>
+      <c r="B22" cm="1">
+        <f t="array" ref="B22:G37">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(Raw_Data[[Sl. No]:[Country]],COUNTIFS(Raw_Data[Name of Incident],Raw_Data[Name of Incident],Raw_Data[Year],Raw_Data[Year],Raw_Data[Country],Raw_Data[Country])&gt;1),2)</f>
+        <v>436</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Battle of Điện Biên Phủ</v>
+      </c>
+      <c r="D22" t="str">
+        <v>7</v>
+      </c>
+      <c r="E22" t="str">
+        <v>May</v>
+      </c>
+      <c r="F22" t="str">
+        <v>1954</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Vietnam</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>474</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Battle of Điện Biên Phủ</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F23" t="str">
+        <v>1954</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Vietnam</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>160</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Cultural Revolution</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F24" t="str">
+        <v>1966</v>
+      </c>
+      <c r="G24" t="str">
+        <v>China</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>193</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Cultural Revolution</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F25" t="str">
+        <v>1966</v>
+      </c>
+      <c r="G25" t="str">
+        <v>China</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>730</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Discovery of Insulin</v>
+      </c>
+      <c r="D26" t="str">
+        <v>27</v>
+      </c>
+      <c r="E26" t="str">
+        <v>July</v>
+      </c>
+      <c r="F26" t="str">
+        <v>1921</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>754</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Discovery of Insulin</v>
+      </c>
+      <c r="D27" t="str">
+        <v>27</v>
+      </c>
+      <c r="E27" t="str">
+        <v>July</v>
+      </c>
+      <c r="F27" t="str">
+        <v>1921</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>743</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Establishment of Nunavut</v>
+      </c>
+      <c r="D28" t="str">
+        <v>1</v>
+      </c>
+      <c r="E28" t="str">
+        <v>April</v>
+      </c>
+      <c r="F28" t="str">
+        <v>1999</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>759</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Establishment of Nunavut</v>
+      </c>
+      <c r="D29" t="str">
+        <v>1</v>
+      </c>
+      <c r="E29" t="str">
+        <v>April</v>
+      </c>
+      <c r="F29" t="str">
+        <v>1999</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>305</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Fukushima Daiichi Nuclear Disaster</v>
+      </c>
+      <c r="D30" t="str">
+        <v>11</v>
+      </c>
+      <c r="E30" t="str">
+        <v>March</v>
+      </c>
+      <c r="F30" t="str">
+        <v>2011</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Japan</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>649</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Fukushima Daiichi Nuclear Disaster</v>
+      </c>
+      <c r="D31" t="str">
+        <v>11</v>
+      </c>
+      <c r="E31" t="str">
+        <v>March</v>
+      </c>
+      <c r="F31" t="str">
+        <v>2011</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Japan</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>733</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Official Languages Act</v>
+      </c>
+      <c r="D32" t="str">
+        <v>9</v>
+      </c>
+      <c r="E32" t="str">
+        <v>September</v>
+      </c>
+      <c r="F32" t="str">
+        <v>1969</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <v>757</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Official Languages Act</v>
+      </c>
+      <c r="D33" t="str">
+        <v>9</v>
+      </c>
+      <c r="E33" t="str">
+        <v>September</v>
+      </c>
+      <c r="F33" t="str">
+        <v>1969</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>337</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Port Arthur Massacre</v>
+      </c>
+      <c r="D34" t="str">
+        <v>28</v>
+      </c>
+      <c r="E34" t="str">
+        <v>April</v>
+      </c>
+      <c r="F34" t="str">
+        <v>1996</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>348</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Port Arthur Massacre</v>
+      </c>
+      <c r="D35" t="str">
+        <v>28</v>
+      </c>
+      <c r="E35" t="str">
+        <v>April</v>
+      </c>
+      <c r="F35" t="str">
+        <v>1996</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>333</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Sydney Opera House Opens</v>
+      </c>
+      <c r="D36" t="str">
+        <v>20</v>
+      </c>
+      <c r="E36" t="str">
+        <v>October</v>
+      </c>
+      <c r="F36" t="str">
+        <v>1973</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>344</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Sydney Opera House Opens</v>
+      </c>
+      <c r="D37" t="str">
+        <v>20</v>
+      </c>
+      <c r="E37" t="str">
+        <v>October</v>
+      </c>
+      <c r="F37" t="str">
+        <v>1973</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Australia</v>
       </c>
     </row>
   </sheetData>
